--- a/data/vendor_template.xlsx
+++ b/data/vendor_template.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -627,9 +627,9 @@
       <c r="B19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>문의</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>에러 상세자료 (선택)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr"/>
@@ -637,6 +637,50 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>• 상세설명 : 에러로그 행마다 추가로 길게 적고 싶은 분석/경위. 대시보드의 [＋상세] 버튼에서만 보입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>• 사진(파일명) : 첨부할 이미지 파일명을 쉼표로 구분해 적습니다. 예) ERR-001_1.jpg, ERR-001_2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └ 사진 파일 자체는 엑셀에 붙이지 말고, 파일명만 적은 뒤 이미지 파일들을 엑셀과 함께 PM에게 전달하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └ PM이 data/errors/ 폴더에 같은 이름으로 넣으면 [＋상세]에서 표시됩니다. (미입력 시 버튼은 표시되지 않음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>양식 변경·문제 발생 시 PM에게 문의.</t>
         </is>
@@ -778,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -792,6 +836,9 @@
     <col width="44" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="54" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -847,7 +894,22 @@
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
-          <t>담당</t>
+          <t>삼성 담당자</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>업체 담당자</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>상세설명</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>사진(파일명)</t>
         </is>
       </c>
     </row>
@@ -900,7 +962,22 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
+          <t>양희두</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
           <t>박영희</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>현장 조도 320→210 LUX로 급감한 구간에서 반복 발생. 노출 보정 후 재현 안 됨. (상세 분석 리포트 별첨)</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>ERR-001_1.jpg, ERR-001_2.jpg</t>
         </is>
       </c>
     </row>
@@ -953,7 +1030,22 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
+          <t>김현일</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
           <t>홍길동</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>코팅 로트 편차로 마찰계수 0.4→0.28. 압력 상향으로 해결.</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>ERR-002_grip.png</t>
         </is>
       </c>
     </row>

--- a/data/vendor_template.xlsx
+++ b/data/vendor_template.xlsx
@@ -11,7 +11,10 @@
     <sheet name="일일평가" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="에러로그" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'일일평가'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에러로그'!$A$1:$N$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,23 +33,25 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000C1B36"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00BFD8F2"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000F2E54"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <color rgb="003D4147"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="001A2942"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -57,11 +62,16 @@
     <font>
       <name val="맑은 고딕"/>
       <i val="1"/>
-      <color rgb="007B8087"/>
+      <color rgb="008092A8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="002B3A4F"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -70,16 +80,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000C1B36"/>
+        <fgColor rgb="000F2E54"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F2"/>
+        <fgColor rgb="00EAF2FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E4A7A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F9FE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -88,35 +113,66 @@
       <diagonal/>
     </border>
     <border>
+      <bottom style="thin">
+        <color rgb="002E89D6"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="00D6D2C4"/>
+        <color rgb="00C9DAEE"/>
       </left>
       <right style="thin">
-        <color rgb="00D6D2C4"/>
+        <color rgb="00C9DAEE"/>
       </right>
       <top style="thin">
-        <color rgb="00D6D2C4"/>
+        <color rgb="00C9DAEE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002E89D6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9DAEE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9DAEE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9DAEE"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D6D2C4"/>
+        <color rgb="00C9DAEE"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,214 +537,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002E89D6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>로봇 자동화 양산평가 — 일일 입력 양식</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+          <t>Chemical Drum 체결/반송 자동화 · 양산평가 입력 양식</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PRODUCTION EVALUATION — VENDOR INPUT TEMPLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>작성 방법</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>1) 본 파일은 양식이며, 매일 평가가 끝나면 [일일평가] 시트에 1행씩 추가합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2) 에러가 발생한 날에는 [에러로그] 시트에도 해당 에러 1건을 별도로 추가합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr">
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>1) 본 파일은 양식입니다. 매일 평가가 끝나면 [일일평가] 시트에 1행씩 추가하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2) 에러가 발생한 날에는 [에러로그] 시트에도 해당 에러 1건을 별도로 추가하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>3) 파일명은 자유 (예: 양산평가_2026-06-17.xlsx). 한 파일에 누적 기록을 유지하세요.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>4) 작성 완료한 파일을 PM에게 전달하면 GitHub의 data/raw/ 폴더에 업로드됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="8" ht="19" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>4) 작성 완료한 파일을 PM에게 전달하면 대시보드에 반영됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>주의사항</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr">
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>• 시트명(일일평가 / 에러로그)은 변경하지 마세요.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>• 헤더 행(파란색)은 그대로 유지하세요. 컬럼 순서·이름이 바뀌면 자동 변환이 실패합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>• 날짜는 YYYY-MM-DD 형식 (예: 2026-06-17). 시각은 HH:MM (예: 14:32).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>• 회색 이탤릭 예시 행은 참고용이며, 실제 데이터 입력 시 덮어쓰거나 위에 추가하세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="12" ht="19" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>• 파란 헤더 행은 그대로 유지하세요. 컬럼 이름이 바뀌면 자동 변환이 실패합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>• 날짜는 YYYY-MM-DD (예: 2026-06-17), 시각은 h:mm (예: 14:32).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>• 옅은 파란색 이탤릭 '예시' 행은 참고용입니다. 실제 입력 시 덮어쓰거나 아래 빈 행에 추가하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>핵심 메트릭</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr">
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>• 일일평가 : 그 날 수행한 총 사이클 횟수 (성공+실패 모두 포함)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18" ht="19" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>• 일일에러 : 그 날 발생한 에러(인시던트) 횟수</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr">
+    <row r="19" ht="19" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>• 연속성공 : 마지막 에러 이후 누적 성공 사이클 수</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>에러 상세자료 (선택)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>• 상세설명 : 에러로그 행마다 추가로 길게 적고 싶은 분석/경위. 대시보드의 [＋상세] 버튼에서만 보입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>• 사진(파일명) : 첨부할 이미지 파일명을 쉼표로 구분해 적습니다. 예) ERR-001_1.jpg, ERR-001_2.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └ 사진 파일 자체는 엑셀에 붙이지 말고, 파일명만 적은 뒤 이미지 파일들을 엑셀과 함께 PM에게 전달하세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └ PM이 data/errors/ 폴더에 같은 이름으로 넣으면 [＋상세]에서 표시됩니다. (미입력 시 버튼은 표시되지 않음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>• 상세설명 : 에러 행마다 길게 적고 싶은 분석/경위. 대시보드 [＋상세] 버튼에서만 보입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>• 사진(파일명) : 첨부 이미지 '파일명'만 쉼표로 구분해 적습니다. 예) ERR-001_1.jpg, ERR-001_2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └ 사진은 엑셀에 붙이지 말고, 파일명만 적은 뒤 이미지 파일을 엑셀과 함께(zip) 전달하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └ 두 칸 모두 비워두면 [＋상세] 버튼은 표시되지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>문의</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>양식 변경·문제 발생 시 PM에게 문의.</t>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>양식 변경·문제 발생 시 PM에게 문의하세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="7">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A27:B27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -697,22 +726,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E4A7A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>평가일</t>
@@ -749,7 +779,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2026-06-01</t>
@@ -776,11 +806,11 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>초기 셋업, 안정</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
+          <t>← 예시 (덮어쓰거나 아래에 입력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -807,11 +837,156 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>정상</t>
-        </is>
-      </c>
+          <t>← 예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -819,10 +994,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E4A7A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -831,17 +1007,17 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="54" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>No</t>
@@ -913,7 +1089,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
@@ -952,7 +1128,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>조명 LUX 재조정 + 비전 알고리즘 threshold 보정</t>
+          <t>조명 LUX 재조정 + 비전 threshold 보정</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -972,7 +1148,7 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>현장 조도 320→210 LUX로 급감한 구간에서 반복 발생. 노출 보정 후 재현 안 됨. (상세 분석 리포트 별첨)</t>
+          <t>현장 조도 320→210 LUX 급감 구간에서 반복. 노출 보정 후 재현 안 됨. (분석 리포트 별첨)</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
@@ -981,7 +1157,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="38" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
@@ -1020,7 +1196,7 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>그리퍼 압력 +5% 조정, 부품 표면 사전 검사 단계 추가</t>
+          <t>그리퍼 압력 +5% 조정, 표면 사전검사 추가</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
@@ -1040,7 +1216,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>코팅 로트 편차로 마찰계수 0.4→0.28. 압력 상향으로 해결.</t>
+          <t>코팅 로트 편차로 마찰계수 0.40→0.28. 압력 상향으로 해결.</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -1049,7 +1225,232 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
+      <c r="N4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>